--- a/artfynd/A 30552-2026 artfynd.xlsx
+++ b/artfynd/A 30552-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134983045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134982828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134983091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134982870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134983095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134983077</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134982865</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134982884</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,8 +1632,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134983079</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30552-2026 artfynd.xlsx
+++ b/artfynd/A 30552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134983045</v>
       </c>
       <c r="B2" t="n">
-        <v>75430</v>
+        <v>75466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134982828</v>
       </c>
       <c r="B3" t="n">
-        <v>75354</v>
+        <v>75387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>134983091</v>
       </c>
       <c r="B4" t="n">
-        <v>75354</v>
+        <v>75387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>134982870</v>
       </c>
       <c r="B5" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>134983095</v>
       </c>
       <c r="B6" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>134983077</v>
       </c>
       <c r="B7" t="n">
-        <v>99960</v>
+        <v>100007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>134982865</v>
       </c>
       <c r="B8" t="n">
-        <v>98277</v>
+        <v>98321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>134982884</v>
       </c>
       <c r="B9" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>134983079</v>
       </c>
       <c r="B10" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30552-2026 artfynd.xlsx
+++ b/artfynd/A 30552-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134983045</v>
       </c>
       <c r="B2" t="n">
-        <v>75466</v>
+        <v>75493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134982828</v>
       </c>
       <c r="B3" t="n">
-        <v>75387</v>
+        <v>75414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>134983091</v>
       </c>
       <c r="B4" t="n">
-        <v>75387</v>
+        <v>75414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>134982870</v>
       </c>
       <c r="B5" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>134983095</v>
       </c>
       <c r="B6" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>134983077</v>
       </c>
       <c r="B7" t="n">
-        <v>100007</v>
+        <v>100034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>134982865</v>
       </c>
       <c r="B8" t="n">
-        <v>98321</v>
+        <v>98348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>134982884</v>
       </c>
       <c r="B9" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>134983079</v>
       </c>
       <c r="B10" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
